--- a/data/raw/inventory/Week 34/Nexlev/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 34/Nexlev/Seller FBA Inventory (SP-API).xlsx
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F10" t="n">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -1031,10 +1031,10 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="L10" t="n">
         <v>3</v>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>350</v>
+        <v>399</v>
       </c>
       <c r="F11" t="n">
-        <v>259</v>
+        <v>309</v>
       </c>
       <c r="G11" t="n">
         <v>11</v>
@@ -1093,13 +1093,13 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K11" t="n">
-        <v>366</v>
+        <v>412</v>
       </c>
       <c r="L11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M11" t="n">
         <v>3</v>
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="F17" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G17" t="n">
         <v>166</v>
@@ -1465,10 +1465,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K17" t="n">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="L17" t="n">
         <v>4</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>149</v>
       </c>
       <c r="F20" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>192</v>
+        <v>116</v>
       </c>
       <c r="K20" t="n">
-        <v>210</v>
+        <v>149</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1701,7 +1701,7 @@
         <v>73</v>
       </c>
       <c r="F21" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>73</v>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F22" t="n">
         <v>47</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1949,7 +1949,7 @@
         <v>6</v>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1961,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>7</v>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="F26" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2023,10 +2023,10 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="F27" t="n">
         <v>25</v>
@@ -2085,10 +2085,10 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="K27" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F28" t="n">
         <v>151</v>
@@ -2147,10 +2147,10 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F29" t="n">
         <v>9</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
@@ -2395,10 +2395,10 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="K32" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>304</v>
+        <v>331</v>
       </c>
       <c r="F33" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -2457,10 +2457,10 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="K33" t="n">
-        <v>308</v>
+        <v>335</v>
       </c>
       <c r="L33" t="n">
         <v>4</v>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="F34" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -2519,10 +2519,10 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K34" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F35" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2584,7 +2584,7 @@
         <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F36" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K36" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F37" t="n">
         <v>156</v>
@@ -2705,10 +2705,10 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F38" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -2767,10 +2767,10 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>71</v>
       </c>
       <c r="F41" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G41" t="n">
         <v>4</v>
@@ -2953,13 +2953,13 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
         <v>1</v>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F42" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3015,10 +3015,10 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K42" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F44" t="n">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -3139,10 +3139,10 @@
         <v>12</v>
       </c>
       <c r="J44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K44" t="n">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="L44" t="n">
         <v>7</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F46" t="n">
         <v>30</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L46" t="n">
         <v>2</v>
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F49" t="n">
         <v>30</v>
@@ -3449,10 +3449,10 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -4302,10 +4302,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F63" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -4320,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>396</v>
+        <v>477</v>
       </c>
       <c r="F64" t="n">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -4379,13 +4379,13 @@
         <v>2</v>
       </c>
       <c r="J64" t="n">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="K64" t="n">
-        <v>399</v>
+        <v>479</v>
       </c>
       <c r="L64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M64" t="n">
         <v>1</v>
@@ -4550,13 +4550,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>447</v>
+        <v>937</v>
       </c>
       <c r="F67" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G67" t="n">
-        <v>100</v>
+        <v>596</v>
       </c>
       <c r="H67" t="n">
         <v>300</v>
@@ -4565,13 +4565,13 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K67" t="n">
-        <v>477</v>
+        <v>963</v>
       </c>
       <c r="L67" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="M67" t="n">
         <v>3</v>
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F72" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -4875,10 +4875,10 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -4987,7 +4987,7 @@
         <v>28</v>
       </c>
       <c r="F74" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -4999,7 +4999,7 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="n">
         <v>28</v>
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
         <v>3</v>
@@ -5123,13 +5123,13 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K76" t="n">
-        <v>1479</v>
+        <v>1464</v>
       </c>
       <c r="L76" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F78" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -5247,10 +5247,10 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K78" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -5433,10 +5433,10 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K81" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -5480,13 +5480,13 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -5498,7 +5498,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>431</v>
       </c>
       <c r="L82" t="n">
         <v>1</v>
@@ -5604,7 +5604,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F84" t="n">
         <v>205</v>
@@ -5619,13 +5619,13 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -5790,7 +5790,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F87" t="n">
         <v>7</v>
@@ -5805,10 +5805,10 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F90" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G90" t="n">
         <v>1</v>
@@ -5991,10 +5991,10 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K90" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -6162,25 +6162,25 @@
         </is>
       </c>
       <c r="E93" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" t="n">
         <v>2</v>
-      </c>
-      <c r="F93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" t="n">
-        <v>2</v>
-      </c>
-      <c r="K93" t="n">
-        <v>3</v>
       </c>
       <c r="L93" t="n">
         <v>1</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F97" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -6428,7 +6428,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L97" t="n">
         <v>1</v>
@@ -6490,10 +6490,10 @@
         <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L98" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M98" t="n">
         <v>1</v>
@@ -6534,25 +6534,25 @@
         </is>
       </c>
       <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
         <v>1</v>
-      </c>
-      <c r="F99" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" t="n">
-        <v>1</v>
-      </c>
-      <c r="K99" t="n">
-        <v>2</v>
       </c>
       <c r="L99" t="n">
         <v>1</v>
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F104" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K104" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="L104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
         <v>1</v>
@@ -6906,13 +6906,13 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>234</v>
+        <v>358</v>
       </c>
       <c r="F105" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G105" t="n">
-        <v>3</v>
+        <v>131</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -6921,13 +6921,13 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K105" t="n">
-        <v>237</v>
+        <v>360</v>
       </c>
       <c r="L105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>378</v>
+        <v>325</v>
       </c>
       <c r="F106" t="n">
         <v>320</v>
@@ -6983,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="K106" t="n">
-        <v>378</v>
+        <v>325</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -7092,10 +7092,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -7110,7 +7110,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -7278,13 +7278,13 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>88</v>
+        <v>888</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>80</v>
+        <v>880</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -7296,10 +7296,10 @@
         <v>3</v>
       </c>
       <c r="K111" t="n">
-        <v>97</v>
+        <v>896</v>
       </c>
       <c r="L111" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M111" t="n">
         <v>1</v>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F112" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -7355,10 +7355,10 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K112" t="n">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="L112" t="n">
         <v>1</v>
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F113" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -7420,7 +7420,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -7464,10 +7464,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F114" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -7482,7 +7482,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -7526,13 +7526,13 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>6</v>
+        <v>310</v>
       </c>
       <c r="L115" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M115" t="n">
         <v>0</v>
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F116" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -7606,7 +7606,7 @@
         <v>1</v>
       </c>
       <c r="K116" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -7839,7 +7839,7 @@
         <v>46</v>
       </c>
       <c r="F120" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -7860,7 +7860,7 @@
         <v>3</v>
       </c>
       <c r="M120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>208</v>
+        <v>269</v>
       </c>
       <c r="F128" t="n">
-        <v>206</v>
+        <v>267</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -8350,10 +8350,10 @@
         <v>1</v>
       </c>
       <c r="K128" t="n">
-        <v>209</v>
+        <v>269</v>
       </c>
       <c r="L128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
         <v>1</v>
@@ -8394,7 +8394,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F129" t="n">
         <v>80</v>
@@ -8409,10 +8409,10 @@
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F130" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
         <v>1</v>
       </c>
       <c r="K130" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L130" t="n">
         <v>1</v>
@@ -8645,7 +8645,7 @@
         <v>348</v>
       </c>
       <c r="F133" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G133" t="n">
         <v>36</v>
@@ -8657,7 +8657,7 @@
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K133" t="n">
         <v>350</v>
@@ -8952,7 +8952,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F138" t="n">
         <v>4</v>
@@ -8967,10 +8967,10 @@
         <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K138" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -9091,10 +9091,10 @@
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K140" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F145" t="n">
         <v>0</v>
@@ -9401,10 +9401,10 @@
         <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K145" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -9448,10 +9448,10 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F146" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -9463,10 +9463,10 @@
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K146" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -9634,10 +9634,10 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F149" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -9649,10 +9649,10 @@
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K149" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -9820,10 +9820,10 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -9835,10 +9835,10 @@
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K152" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="F157" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="K157" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F159" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -10269,10 +10269,10 @@
         <v>5</v>
       </c>
       <c r="J159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K159" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -10378,7 +10378,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
@@ -10393,10 +10393,10 @@
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K161" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -10440,13 +10440,13 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>162</v>
+        <v>235</v>
       </c>
       <c r="F162" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G162" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="H162" t="n">
         <v>96</v>
@@ -10458,7 +10458,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>162</v>
+        <v>235</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -10688,7 +10688,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>
@@ -10703,10 +10703,10 @@
         <v>0</v>
       </c>
       <c r="J166" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K166" t="n">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="L166" t="n">
         <v>4</v>
@@ -10750,7 +10750,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F167" t="n">
         <v>0</v>
@@ -10765,10 +10765,10 @@
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="K167" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -10812,13 +10812,13 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1</v>
+        <v>131</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -10830,7 +10830,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="n">
-        <v>1</v>
+        <v>131</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F176" t="n">
         <v>32</v>
@@ -11323,10 +11323,10 @@
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K176" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
@@ -11370,13 +11370,13 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F177" t="n">
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -11388,7 +11388,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="L177" t="n">
         <v>1</v>
@@ -11494,7 +11494,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F179" t="n">
         <v>26</v>
@@ -11509,10 +11509,10 @@
         <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K179" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="F180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -11683,19 +11683,19 @@
         <v>1</v>
       </c>
       <c r="F182" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" t="n">
         <v>1</v>
-      </c>
-      <c r="G182" t="n">
-        <v>0</v>
-      </c>
-      <c r="H182" t="n">
-        <v>0</v>
-      </c>
-      <c r="I182" t="n">
-        <v>0</v>
-      </c>
-      <c r="J182" t="n">
-        <v>0</v>
       </c>
       <c r="K182" t="n">
         <v>1</v>
@@ -11866,25 +11866,25 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F185" t="n">
+        <v>46</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0</v>
+      </c>
+      <c r="I185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" t="n">
+        <v>2</v>
+      </c>
+      <c r="K185" t="n">
         <v>48</v>
-      </c>
-      <c r="G185" t="n">
-        <v>0</v>
-      </c>
-      <c r="H185" t="n">
-        <v>0</v>
-      </c>
-      <c r="I185" t="n">
-        <v>0</v>
-      </c>
-      <c r="J185" t="n">
-        <v>1</v>
-      </c>
-      <c r="K185" t="n">
-        <v>49</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>

--- a/data/raw/inventory/Week 34/Nexlev/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 34/Nexlev/Seller FBA Inventory (SP-API).xlsx
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="F10" t="n">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -1034,7 +1034,7 @@
         <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="L10" t="n">
         <v>3</v>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F11" t="n">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G11" t="n">
         <v>11</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L11" t="n">
         <v>13</v>
@@ -1453,7 +1453,7 @@
         <v>1280</v>
       </c>
       <c r="F17" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G17" t="n">
         <v>166</v>
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K17" t="n">
         <v>1284</v>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F34" t="n">
         <v>31</v>
@@ -2519,10 +2519,10 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -3127,7 +3127,7 @@
         <v>363</v>
       </c>
       <c r="F44" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -3139,7 +3139,7 @@
         <v>12</v>
       </c>
       <c r="J44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K44" t="n">
         <v>370</v>
@@ -4553,7 +4553,7 @@
         <v>937</v>
       </c>
       <c r="F67" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G67" t="n">
         <v>596</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K67" t="n">
         <v>963</v>
@@ -4612,13 +4612,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>7</v>
+        <v>607</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>7</v>
+        <v>607</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>7</v>
+        <v>607</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -4798,13 +4798,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -4816,7 +4816,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>721</v>
       </c>
       <c r="L71" t="n">
         <v>1</v>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F90" t="n">
         <v>26</v>
@@ -5991,10 +5991,10 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K90" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F128" t="n">
         <v>267</v>
@@ -8347,10 +8347,10 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F159" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -10272,7 +10272,7 @@
         <v>1</v>
       </c>
       <c r="K159" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
